--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockUpdateTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockUpdateTemplate.xlsx
@@ -1,40 +1,512 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>退货入库单号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>退货客户</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>库存组织</t>
+    </r>
+  </si>
+  <si>
+    <t>币种</t>
+  </si>
+  <si>
+    <t>入库日期</t>
+  </si>
+  <si>
+    <t>单据类型</t>
+  </si>
+  <si>
+    <t>退货物流单号</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
-    <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
-    <fill>
-      <patternFill/>
+  <fills count="34">
+    <fill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.25"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -42,85 +514,330 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -403,57 +1120,61 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="14.75" customWidth="1"/>
+    <col min="2" max="3" width="10.25" customWidth="1"/>
+    <col min="4" max="4" width="5.375" customWidth="1"/>
+    <col min="5" max="6" width="9.375" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>*退货入库单号</t>
-        </is>
+    <row r="1" s="1" customFormat="1" ht="23" customHeight="1" spans="1:13">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>*退货客户</t>
-        </is>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>*库存组织</t>
-        </is>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>币种</t>
-        </is>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>入库日期</t>
-        </is>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>单据类型</t>
-        </is>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>退货物流单号</t>
-        </is>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
       </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:13">
+      <c r="E2" s="6"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2">
+      <formula1>"B2B订单,B2C订单,售后订单-补/换/赠"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockUpdateTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockUpdateTemplate.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="导入填写指南" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <r>
       <rPr>
@@ -111,6 +112,321 @@
   </si>
   <si>
     <t>退货物流单号</t>
+  </si>
+  <si>
+    <t>字段</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退货入库单号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退货客户</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>库存组织</t>
+    </r>
+  </si>
+  <si>
+    <t>是否必填</t>
+  </si>
+  <si>
+    <t>必填</t>
+  </si>
+  <si>
+    <t>必填/选题</t>
+  </si>
+  <si>
+    <t>选填</t>
+  </si>
+  <si>
+    <t>数据获取来源</t>
+  </si>
+  <si>
+    <t>①文本框填入
+②为主键</t>
+  </si>
+  <si>
+    <t>①文本框填入
+②填写客户名称
+③填写的客户必须是《B2C客户》/《B2B客户》表已审核且启用状态
+④已关联“退货订单”则不可更改</t>
+  </si>
+  <si>
+    <t>①下拉框填入
+②填写库存组织
+③填写的库存组织必须是已审核且启用状态</t>
+  </si>
+  <si>
+    <t>①下拉框填入
+②已提供币种选项，可另外增加，但必须是系统已维护的
+③不填默认取原来值</t>
+  </si>
+  <si>
+    <t>①日期选择期
+②仅可填写日期格式
+③不填默认取原来值</t>
+  </si>
+  <si>
+    <t>①下拉框填入
+②已提供选项，可另外增加，但必须是系统已维护的
+③不填默认取原来值</t>
+  </si>
+  <si>
+    <t>①文本框填入
+③不填默认取原来值/为空</t>
+  </si>
+  <si>
+    <t>判断说明</t>
+  </si>
+  <si>
+    <r>
+      <t>一、整个表数据导入成功才更新覆盖，否则整个表导入失败；
+二、以“退货入库单号”为key，排重：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1、如果未能找到该key，则报错；
+2、如果找到该key，则覆盖更新
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>三、导入判断内容及提示语：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+1、未能找到退货入库单号-----</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">无法识别退货入库单号，请确定编码是否正确或是否存在
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2、订单条件不可编辑----</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仅有待提交且未作废退货入库单可修改</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+3、客户，未找到/未启动------</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">未能找到客户，请确定客户是否正确/已启用
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>4、客户因条件限制不可更改------</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仅有未映射“退货单号”的退货入库单的客户信息可更新</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+5、库存组织，未找到/未启动-----</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>未能找到库存组织，请确定库存组织是否正确/已启用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+6、币种乱填-----</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>该币种未在系统枚举值找到，请确定是否正确</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+7、单据类型乱填-----</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>该单据类型未在系统枚举值找到，请确定是否正确</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+8、“退货入库单号”key在excel表中重复----</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>退货入库单号在导入表中重复了，请调整（重复行都提醒）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">
+9、入库日期填写错误---</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">入库日期非日期格式，请调整
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -123,7 +439,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -132,11 +448,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="华文仿宋"/>
       <charset val="134"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -305,8 +646,20 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -315,6 +668,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFD8D8D8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.25"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -506,12 +865,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -615,169 +989,199 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1136,37 +1540,37 @@
     <col min="7" max="7" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="23" customHeight="1" spans="1:13">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="11" customFormat="1" ht="23" customHeight="1" spans="1:13">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:13">
-      <c r="E2" s="6"/>
+    <row r="2" s="11" customFormat="1" spans="1:13">
+      <c r="E2" s="16"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1177,4 +1581,114 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="8" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="216" spans="1:8">
+      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" ht="191" customHeight="1" spans="1:8">
+      <c r="A4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockUpdateTemplate.xlsx
+++ b/erp-server/erp-server-wms/src/main/resources/excel/soReturnInstockUpdateTemplate.xlsx
@@ -427,6 +427,24 @@
       <t xml:space="preserve">入库日期非日期格式，请调整
 </t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t>10、部分来源类型不允许修改---</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFC00000"/>
+        <rFont val="华文仿宋"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">仅支持来源“三方仓/手工建单”的退货入库单修改
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -439,7 +457,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -655,6 +673,11 @@
     <font>
       <sz val="10"/>
       <color rgb="FFC00000"/>
+      <name val="华文仿宋"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="华文仿宋"/>
       <charset val="134"/>
     </font>
@@ -1644,7 +1667,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" ht="216" spans="1:8">
+    <row r="3" ht="108" spans="1:8">
       <c r="A3" s="5" t="s">
         <v>15</v>
       </c>
